--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260717.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260717.xlsx
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>65,106,533</t>
+          <t>433,339,383</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>433,339,383</t>
+          <t>65,106,533</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>上海商銀</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>211,180,443</t>
+          <t>2,841,261</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>2,841,261</t>
+          <t>211,180,443</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>信邦</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>32,186,310</t>
+          <t>10,836,888</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>信邦</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>10,836,888</t>
+          <t>32,186,310</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
